--- a/artfynd/A 50126-2024 artfynd.xlsx
+++ b/artfynd/A 50126-2024 artfynd.xlsx
@@ -2182,10 +2182,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121156706</v>
+        <v>121156694</v>
       </c>
       <c r="B15" t="n">
-        <v>90687</v>
+        <v>57348</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2198,40 +2198,49 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Porten, Jmt</t>
+          <t>Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510388</v>
+        <v>510480</v>
       </c>
       <c r="R15" t="n">
-        <v>7001745</v>
+        <v>7001661</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2269,7 +2278,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2290,12 +2298,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2313,10 +2321,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121156694</v>
+        <v>121156706</v>
       </c>
       <c r="B16" t="n">
-        <v>57348</v>
+        <v>90687</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2329,49 +2337,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lillmyren, Jmt</t>
+          <t>Porten, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510480</v>
+        <v>510388</v>
       </c>
       <c r="R16" t="n">
-        <v>7001661</v>
+        <v>7001745</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2409,6 +2408,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2429,12 +2429,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2725,10 +2725,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121156685</v>
+        <v>121099320</v>
       </c>
       <c r="B19" t="n">
-        <v>57364</v>
+        <v>79679</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2741,49 +2741,44 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lillmyren, Jmt</t>
+          <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>510480</v>
+        <v>510339</v>
       </c>
       <c r="R19" t="n">
-        <v>7001661</v>
+        <v>7001763</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2815,17 +2810,13 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska hackspår av spillkråka i basen av en levande granstam och i en kolad stubbe.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2836,22 +2827,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2869,10 +2860,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121099320</v>
+        <v>121156685</v>
       </c>
       <c r="B20" t="n">
-        <v>79679</v>
+        <v>57364</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2885,44 +2876,49 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Porten, Porten, Jmt</t>
+          <t>Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>510339</v>
+        <v>510480</v>
       </c>
       <c r="R20" t="n">
-        <v>7001763</v>
+        <v>7001661</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2954,13 +2950,17 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska hackspår av spillkråka i basen av en levande granstam och i en kolad stubbe.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2971,22 +2971,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 50126-2024 artfynd.xlsx
+++ b/artfynd/A 50126-2024 artfynd.xlsx
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121098199</v>
+        <v>121097354</v>
       </c>
       <c r="B3" t="n">
-        <v>90973</v>
+        <v>90715</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,21 +819,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510513</v>
+        <v>510507</v>
       </c>
       <c r="R3" t="n">
-        <v>7001652</v>
+        <v>7001641</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121099202</v>
+        <v>121098199</v>
       </c>
       <c r="B4" t="n">
-        <v>78334</v>
+        <v>90983</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,34 +921,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Porten, Porten, Jmt</t>
+          <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510360</v>
+        <v>510513</v>
       </c>
       <c r="R4" t="n">
-        <v>7001779</v>
+        <v>7001652</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121098323</v>
+        <v>121097284</v>
       </c>
       <c r="B5" t="n">
-        <v>74705</v>
+        <v>57504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,34 +1023,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>510503</v>
+        <v>510508</v>
       </c>
       <c r="R5" t="n">
-        <v>7001630</v>
+        <v>7001663</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121097263</v>
+        <v>121098265</v>
       </c>
       <c r="B6" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510522</v>
+        <v>510510</v>
       </c>
       <c r="R6" t="n">
-        <v>7001662</v>
+        <v>7001653</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121097354</v>
+        <v>121097256</v>
       </c>
       <c r="B7" t="n">
-        <v>90705</v>
+        <v>57351</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,34 +1236,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510507</v>
+        <v>510522</v>
       </c>
       <c r="R7" t="n">
-        <v>7001641</v>
+        <v>7001662</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,6 +1314,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1316,7 +1358,7 @@
         <v>121097307</v>
       </c>
       <c r="B8" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1448,10 +1490,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121097284</v>
+        <v>121098323</v>
       </c>
       <c r="B9" t="n">
-        <v>57501</v>
+        <v>74708</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,43 +1506,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510508</v>
+        <v>510503</v>
       </c>
       <c r="R9" t="n">
-        <v>7001663</v>
+        <v>7001630</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,10 +1592,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121097256</v>
+        <v>121097263</v>
       </c>
       <c r="B10" t="n">
-        <v>57348</v>
+        <v>79682</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,32 +1608,24 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lillmyren, Lillmyren, Jmt</t>
@@ -1653,31 +1678,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1694,10 +1694,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121098265</v>
+        <v>121099202</v>
       </c>
       <c r="B11" t="n">
-        <v>79679</v>
+        <v>78337</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1710,34 +1710,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lillmyren, Lillmyren, Jmt</t>
+          <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510510</v>
+        <v>510360</v>
       </c>
       <c r="R11" t="n">
-        <v>7001653</v>
+        <v>7001779</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1796,10 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121098825</v>
+        <v>121099320</v>
       </c>
       <c r="B12" t="n">
-        <v>91375</v>
+        <v>79682</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1808,38 +1808,34 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>67</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1847,10 +1843,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510388</v>
+        <v>510339</v>
       </c>
       <c r="R12" t="n">
-        <v>7001745</v>
+        <v>7001763</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,22 +1898,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Både med och utan markkontakt. Delen av stammen där sprickporingens fruktkroppar växer ligger ca 2 dm över marken. # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1938,7 +1934,7 @@
         <v>121098269</v>
       </c>
       <c r="B13" t="n">
-        <v>79715</v>
+        <v>79718</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2070,10 +2066,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121097723</v>
+        <v>121099463</v>
       </c>
       <c r="B14" t="n">
-        <v>95618</v>
+        <v>79711</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2082,42 +2078,45 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lillmyren, Lillmyren, Jmt</t>
+          <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510506</v>
+        <v>510317</v>
       </c>
       <c r="R14" t="n">
-        <v>7001644</v>
+        <v>7001784</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2165,6 +2164,26 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2182,10 +2201,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121156694</v>
+        <v>121156706</v>
       </c>
       <c r="B15" t="n">
-        <v>57348</v>
+        <v>90697</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2198,49 +2217,40 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lillmyren, Jmt</t>
+          <t>Porten, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510480</v>
+        <v>510388</v>
       </c>
       <c r="R15" t="n">
-        <v>7001661</v>
+        <v>7001745</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2278,6 +2288,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2298,12 +2309,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2321,10 +2332,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121156706</v>
+        <v>121156694</v>
       </c>
       <c r="B16" t="n">
-        <v>90687</v>
+        <v>57351</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2337,40 +2348,49 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Porten, Jmt</t>
+          <t>Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510388</v>
+        <v>510480</v>
       </c>
       <c r="R16" t="n">
-        <v>7001745</v>
+        <v>7001661</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2408,7 +2428,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2429,12 +2448,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2452,10 +2471,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121099463</v>
+        <v>121156685</v>
       </c>
       <c r="B17" t="n">
-        <v>79708</v>
+        <v>57367</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2464,48 +2483,53 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Porten, Porten, Jmt</t>
+          <t>Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510317</v>
+        <v>510480</v>
       </c>
       <c r="R17" t="n">
-        <v>7001784</v>
+        <v>7001661</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2537,13 +2561,17 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska hackspår av spillkråka i basen av en levande granstam och i en kolad stubbe.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2554,22 +2582,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2590,7 +2618,7 @@
         <v>121156704</v>
       </c>
       <c r="B18" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2725,10 +2753,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121099320</v>
+        <v>121097723</v>
       </c>
       <c r="B19" t="n">
-        <v>79679</v>
+        <v>95628</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2741,41 +2769,38 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Porten, Porten, Jmt</t>
+          <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>510339</v>
+        <v>510506</v>
       </c>
       <c r="R19" t="n">
-        <v>7001763</v>
+        <v>7001644</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2823,26 +2848,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2860,10 +2865,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121156685</v>
+        <v>121098825</v>
       </c>
       <c r="B20" t="n">
-        <v>57364</v>
+        <v>91385</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2872,53 +2877,52 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>67</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lillmyren, Jmt</t>
+          <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>510480</v>
+        <v>510388</v>
       </c>
       <c r="R20" t="n">
-        <v>7001661</v>
+        <v>7001745</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2950,17 +2954,13 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska hackspår av spillkråka i basen av en levande granstam och i en kolad stubbe.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2981,12 +2981,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Både med och utan markkontakt. Delen av stammen där sprickporingens fruktkroppar växer ligger ca 2 dm över marken. # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3004,10 +3004,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121098783</v>
+        <v>121099210</v>
       </c>
       <c r="B21" t="n">
-        <v>90973</v>
+        <v>90662</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3016,25 +3016,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>510388</v>
+        <v>510364</v>
       </c>
       <c r="R21" t="n">
-        <v>7001741</v>
+        <v>7001767</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3097,27 +3097,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3135,10 +3115,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121099090</v>
+        <v>121099190</v>
       </c>
       <c r="B22" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3170,7 +3150,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3195,10 +3175,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>510375</v>
+        <v>510363</v>
       </c>
       <c r="R22" t="n">
-        <v>7001739</v>
+        <v>7001774</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3263,10 +3243,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121098790</v>
+        <v>121098783</v>
       </c>
       <c r="B23" t="n">
-        <v>95618</v>
+        <v>90983</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3279,27 +3259,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3307,10 +3286,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>510395</v>
+        <v>510388</v>
       </c>
       <c r="R23" t="n">
-        <v>7001752</v>
+        <v>7001741</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3360,6 +3339,16 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AM23" t="inlineStr">
         <is>
           <t>Liggande död trädstam, markontakt</t>
@@ -3367,7 +3356,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3385,10 +3374,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121099277</v>
+        <v>121099090</v>
       </c>
       <c r="B24" t="n">
-        <v>74705</v>
+        <v>98081</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3397,41 +3386,58 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>510345</v>
+        <v>510375</v>
       </c>
       <c r="R24" t="n">
-        <v>7001762</v>
+        <v>7001739</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3479,21 +3485,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3511,10 +3502,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121099213</v>
+        <v>121099162</v>
       </c>
       <c r="B25" t="n">
-        <v>78598</v>
+        <v>57504</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3527,37 +3518,50 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>510360</v>
+        <v>510354</v>
       </c>
       <c r="R25" t="n">
-        <v>7001779</v>
+        <v>7001746</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3598,7 +3602,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3622,10 +3625,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121098983</v>
+        <v>121099891</v>
       </c>
       <c r="B26" t="n">
-        <v>90701</v>
+        <v>79683</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3638,21 +3641,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3665,10 +3668,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>510387</v>
+        <v>510301</v>
       </c>
       <c r="R26" t="n">
-        <v>7001741</v>
+        <v>7001726</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3718,14 +3721,19 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3743,10 +3751,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121099190</v>
+        <v>121099111</v>
       </c>
       <c r="B27" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3778,7 +3786,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3803,10 +3811,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>510363</v>
+        <v>510355</v>
       </c>
       <c r="R27" t="n">
-        <v>7001774</v>
+        <v>7001742</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3871,10 +3879,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121099111</v>
+        <v>121098983</v>
       </c>
       <c r="B28" t="n">
-        <v>98071</v>
+        <v>90711</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3883,58 +3891,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>510355</v>
+        <v>510387</v>
       </c>
       <c r="R28" t="n">
-        <v>7001742</v>
+        <v>7001741</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3982,6 +3973,16 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3999,10 +4000,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121099210</v>
+        <v>121099213</v>
       </c>
       <c r="B29" t="n">
-        <v>90652</v>
+        <v>78601</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4011,25 +4012,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4042,10 +4043,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>510364</v>
+        <v>510360</v>
       </c>
       <c r="R29" t="n">
-        <v>7001767</v>
+        <v>7001779</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4110,10 +4111,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121099162</v>
+        <v>121099241</v>
       </c>
       <c r="B30" t="n">
-        <v>57501</v>
+        <v>78601</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4126,50 +4127,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>510354</v>
+        <v>510337</v>
       </c>
       <c r="R30" t="n">
-        <v>7001746</v>
+        <v>7001780</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4210,6 +4198,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4233,10 +4222,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121099241</v>
+        <v>121099277</v>
       </c>
       <c r="B31" t="n">
-        <v>78598</v>
+        <v>74708</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4249,21 +4238,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4276,10 +4265,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>510337</v>
+        <v>510345</v>
       </c>
       <c r="R31" t="n">
-        <v>7001780</v>
+        <v>7001762</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4327,6 +4316,21 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4344,10 +4348,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121099891</v>
+        <v>121098578</v>
       </c>
       <c r="B32" t="n">
-        <v>79680</v>
+        <v>95628</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4360,26 +4364,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>53</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4387,10 +4392,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>510301</v>
+        <v>510428</v>
       </c>
       <c r="R32" t="n">
-        <v>7001726</v>
+        <v>7001712</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4440,19 +4445,14 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4470,10 +4470,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121098578</v>
+        <v>121098790</v>
       </c>
       <c r="B33" t="n">
-        <v>95618</v>
+        <v>95628</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>510428</v>
+        <v>510395</v>
       </c>
       <c r="R33" t="n">
-        <v>7001712</v>
+        <v>7001752</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">

--- a/artfynd/A 50126-2024 artfynd.xlsx
+++ b/artfynd/A 50126-2024 artfynd.xlsx
@@ -1118,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121098265</v>
+        <v>121097256</v>
       </c>
       <c r="B6" t="n">
-        <v>79682</v>
+        <v>57351</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,34 +1134,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510510</v>
+        <v>510522</v>
       </c>
       <c r="R6" t="n">
-        <v>7001653</v>
+        <v>7001662</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,6 +1212,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1220,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121097256</v>
+        <v>121098265</v>
       </c>
       <c r="B7" t="n">
-        <v>57351</v>
+        <v>79682</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,42 +1269,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510522</v>
+        <v>510510</v>
       </c>
       <c r="R7" t="n">
-        <v>7001662</v>
+        <v>7001653</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,31 +1339,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">

--- a/artfynd/A 50126-2024 artfynd.xlsx
+++ b/artfynd/A 50126-2024 artfynd.xlsx
@@ -1118,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121097256</v>
+        <v>121098265</v>
       </c>
       <c r="B6" t="n">
-        <v>57351</v>
+        <v>79682</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,42 +1134,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510522</v>
+        <v>510510</v>
       </c>
       <c r="R6" t="n">
-        <v>7001662</v>
+        <v>7001653</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,31 +1204,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1253,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121098265</v>
+        <v>121097256</v>
       </c>
       <c r="B7" t="n">
-        <v>79682</v>
+        <v>57351</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,34 +1236,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510510</v>
+        <v>510522</v>
       </c>
       <c r="R7" t="n">
-        <v>7001653</v>
+        <v>7001662</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,6 +1314,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">

--- a/artfynd/A 50126-2024 artfynd.xlsx
+++ b/artfynd/A 50126-2024 artfynd.xlsx
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121097354</v>
+        <v>121098199</v>
       </c>
       <c r="B3" t="n">
-        <v>90715</v>
+        <v>90983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,21 +819,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510507</v>
+        <v>510513</v>
       </c>
       <c r="R3" t="n">
-        <v>7001641</v>
+        <v>7001652</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121098199</v>
+        <v>121098323</v>
       </c>
       <c r="B4" t="n">
-        <v>90983</v>
+        <v>74708</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,21 +921,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510513</v>
+        <v>510503</v>
       </c>
       <c r="R4" t="n">
-        <v>7001652</v>
+        <v>7001630</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121097284</v>
+        <v>121097307</v>
       </c>
       <c r="B5" t="n">
-        <v>57504</v>
+        <v>57351</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,43 +1023,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>510508</v>
+        <v>510514</v>
       </c>
       <c r="R5" t="n">
-        <v>7001663</v>
+        <v>7001648</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,6 +1101,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1118,7 +1142,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121098265</v>
+        <v>121097263</v>
       </c>
       <c r="B6" t="n">
         <v>79682</v>
@@ -1158,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510510</v>
+        <v>510522</v>
       </c>
       <c r="R6" t="n">
-        <v>7001653</v>
+        <v>7001662</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1355,10 +1379,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121097307</v>
+        <v>121098265</v>
       </c>
       <c r="B8" t="n">
-        <v>57351</v>
+        <v>79682</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,42 +1395,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510514</v>
+        <v>510510</v>
       </c>
       <c r="R8" t="n">
-        <v>7001648</v>
+        <v>7001653</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1449,31 +1465,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1490,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121098323</v>
+        <v>121097354</v>
       </c>
       <c r="B9" t="n">
-        <v>74708</v>
+        <v>90715</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,21 +1497,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1530,10 +1521,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510503</v>
+        <v>510507</v>
       </c>
       <c r="R9" t="n">
-        <v>7001630</v>
+        <v>7001641</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1592,10 +1583,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121097263</v>
+        <v>121097284</v>
       </c>
       <c r="B10" t="n">
-        <v>79682</v>
+        <v>57504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,34 +1599,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510522</v>
+        <v>510508</v>
       </c>
       <c r="R10" t="n">
-        <v>7001662</v>
+        <v>7001663</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1796,10 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121099320</v>
+        <v>121098269</v>
       </c>
       <c r="B12" t="n">
-        <v>79682</v>
+        <v>79718</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1808,45 +1808,45 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Porten, Porten, Jmt</t>
+          <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510339</v>
+        <v>510487</v>
       </c>
       <c r="R12" t="n">
-        <v>7001763</v>
+        <v>7001652</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1931,10 +1931,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121098269</v>
+        <v>121156706</v>
       </c>
       <c r="B13" t="n">
-        <v>79718</v>
+        <v>90697</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,45 +1943,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lillmyren, Lillmyren, Jmt</t>
+          <t>Porten, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510487</v>
+        <v>510388</v>
       </c>
       <c r="R13" t="n">
-        <v>7001652</v>
+        <v>7001745</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2033,22 +2029,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2066,10 +2062,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121099463</v>
+        <v>121098825</v>
       </c>
       <c r="B14" t="n">
-        <v>79711</v>
+        <v>91385</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2078,34 +2074,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>67</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510317</v>
+        <v>510388</v>
       </c>
       <c r="R14" t="n">
-        <v>7001784</v>
+        <v>7001745</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2168,22 +2168,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead without ground contact # Både med och utan markkontakt. Delen av stammen där sprickporingens fruktkroppar växer ligger ca 2 dm över marken. # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2201,10 +2201,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121156706</v>
+        <v>121156704</v>
       </c>
       <c r="B15" t="n">
-        <v>90697</v>
+        <v>98081</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2213,41 +2213,58 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Porten, Jmt</t>
+          <t>Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510388</v>
+        <v>510486</v>
       </c>
       <c r="R15" t="n">
-        <v>7001745</v>
+        <v>7001664</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2282,6 +2299,11 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Minst 170 st. skott/stjälkar och 6 st. fröställningar av knärot inom ca 1 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2297,24 +2319,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2332,10 +2339,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121156694</v>
+        <v>121156685</v>
       </c>
       <c r="B16" t="n">
-        <v>57351</v>
+        <v>57367</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2348,16 +2355,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2370,7 +2377,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2420,6 +2427,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska hackspår av spillkråka i basen av en levande granstam och i en kolad stubbe.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2471,10 +2483,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121156685</v>
+        <v>121099463</v>
       </c>
       <c r="B17" t="n">
-        <v>57367</v>
+        <v>79711</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2483,53 +2495,48 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lillmyren, Jmt</t>
+          <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510480</v>
+        <v>510317</v>
       </c>
       <c r="R17" t="n">
-        <v>7001661</v>
+        <v>7001784</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2561,17 +2568,13 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska hackspår av spillkråka i basen av en levande granstam och i en kolad stubbe.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2582,22 +2585,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2615,10 +2618,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121156704</v>
+        <v>121156694</v>
       </c>
       <c r="B18" t="n">
-        <v>98081</v>
+        <v>57351</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2627,43 +2630,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2675,13 +2670,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>510486</v>
+        <v>510480</v>
       </c>
       <c r="R18" t="n">
-        <v>7001664</v>
+        <v>7001661</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2713,18 +2708,12 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Minst 170 st. skott/stjälkar och 6 st. fröställningar av knärot inom ca 1 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2733,9 +2722,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>På frisk och frisk-fuktig mark.</t>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2753,10 +2757,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121097723</v>
+        <v>121099320</v>
       </c>
       <c r="B19" t="n">
-        <v>95628</v>
+        <v>79682</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2769,38 +2773,41 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lillmyren, Lillmyren, Jmt</t>
+          <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>510506</v>
+        <v>510339</v>
       </c>
       <c r="R19" t="n">
-        <v>7001644</v>
+        <v>7001763</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2848,6 +2855,26 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2865,10 +2892,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121098825</v>
+        <v>121097723</v>
       </c>
       <c r="B20" t="n">
-        <v>91385</v>
+        <v>95628</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2877,49 +2904,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Porten, Porten, Jmt</t>
+          <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>510388</v>
+        <v>510506</v>
       </c>
       <c r="R20" t="n">
-        <v>7001745</v>
+        <v>7001644</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2967,26 +2987,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Både med och utan markkontakt. Delen av stammen där sprickporingens fruktkroppar växer ligger ca 2 dm över marken. # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3004,10 +3004,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121099210</v>
+        <v>121098578</v>
       </c>
       <c r="B21" t="n">
-        <v>90662</v>
+        <v>95628</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3016,30 +3016,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3047,10 +3048,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>510364</v>
+        <v>510428</v>
       </c>
       <c r="R21" t="n">
-        <v>7001767</v>
+        <v>7001712</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3098,6 +3099,16 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3115,10 +3126,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121099190</v>
+        <v>121099891</v>
       </c>
       <c r="B22" t="n">
-        <v>98081</v>
+        <v>79683</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3127,58 +3138,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>510363</v>
+        <v>510301</v>
       </c>
       <c r="R22" t="n">
-        <v>7001774</v>
+        <v>7001726</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3226,6 +3220,21 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3243,10 +3252,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121098783</v>
+        <v>121099111</v>
       </c>
       <c r="B23" t="n">
-        <v>90983</v>
+        <v>98081</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3255,41 +3264,58 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>510388</v>
+        <v>510355</v>
       </c>
       <c r="R23" t="n">
-        <v>7001741</v>
+        <v>7001742</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3336,27 +3362,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3374,10 +3380,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121099090</v>
+        <v>121098783</v>
       </c>
       <c r="B24" t="n">
-        <v>98081</v>
+        <v>90983</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3386,58 +3392,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>510375</v>
+        <v>510388</v>
       </c>
       <c r="R24" t="n">
-        <v>7001739</v>
+        <v>7001741</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3484,7 +3473,27 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3625,10 +3634,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121099891</v>
+        <v>121099210</v>
       </c>
       <c r="B26" t="n">
-        <v>79683</v>
+        <v>90662</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3637,25 +3646,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3668,10 +3677,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>510301</v>
+        <v>510364</v>
       </c>
       <c r="R26" t="n">
-        <v>7001726</v>
+        <v>7001767</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3719,21 +3728,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3751,10 +3745,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121099111</v>
+        <v>121099277</v>
       </c>
       <c r="B27" t="n">
-        <v>98081</v>
+        <v>74708</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3763,58 +3757,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>510355</v>
+        <v>510345</v>
       </c>
       <c r="R27" t="n">
-        <v>7001742</v>
+        <v>7001762</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3862,6 +3839,21 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4000,10 +3992,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121099213</v>
+        <v>121098790</v>
       </c>
       <c r="B29" t="n">
-        <v>78601</v>
+        <v>95628</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4016,26 +4008,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4043,10 +4036,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>510360</v>
+        <v>510395</v>
       </c>
       <c r="R29" t="n">
-        <v>7001779</v>
+        <v>7001752</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4093,7 +4086,17 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4111,10 +4114,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121099241</v>
+        <v>121099190</v>
       </c>
       <c r="B30" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4123,41 +4126,58 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>510337</v>
+        <v>510363</v>
       </c>
       <c r="R30" t="n">
-        <v>7001780</v>
+        <v>7001774</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4222,10 +4242,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121099277</v>
+        <v>121099090</v>
       </c>
       <c r="B31" t="n">
-        <v>74708</v>
+        <v>98081</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4234,41 +4254,58 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>510345</v>
+        <v>510375</v>
       </c>
       <c r="R31" t="n">
-        <v>7001762</v>
+        <v>7001739</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4316,21 +4353,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4348,10 +4370,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121098578</v>
+        <v>121099241</v>
       </c>
       <c r="B32" t="n">
-        <v>95628</v>
+        <v>78601</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4364,27 +4386,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4392,10 +4413,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>510428</v>
+        <v>510337</v>
       </c>
       <c r="R32" t="n">
-        <v>7001712</v>
+        <v>7001780</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4443,16 +4464,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4470,10 +4481,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121098790</v>
+        <v>121099213</v>
       </c>
       <c r="B33" t="n">
-        <v>95628</v>
+        <v>78601</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4486,27 +4497,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4514,10 +4524,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>510395</v>
+        <v>510360</v>
       </c>
       <c r="R33" t="n">
-        <v>7001752</v>
+        <v>7001779</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4564,17 +4574,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>

--- a/artfynd/A 50126-2024 artfynd.xlsx
+++ b/artfynd/A 50126-2024 artfynd.xlsx
@@ -1481,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121097354</v>
+        <v>121097284</v>
       </c>
       <c r="B9" t="n">
-        <v>90715</v>
+        <v>57504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1497,34 +1497,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510507</v>
+        <v>510508</v>
       </c>
       <c r="R9" t="n">
-        <v>7001641</v>
+        <v>7001663</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1583,10 +1592,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121097284</v>
+        <v>121097354</v>
       </c>
       <c r="B10" t="n">
-        <v>57504</v>
+        <v>90715</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1599,43 +1608,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510508</v>
+        <v>510507</v>
       </c>
       <c r="R10" t="n">
-        <v>7001663</v>
+        <v>7001641</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 50126-2024 artfynd.xlsx
+++ b/artfynd/A 50126-2024 artfynd.xlsx
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121098199</v>
+        <v>121097256</v>
       </c>
       <c r="B3" t="n">
-        <v>90983</v>
+        <v>57351</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,34 +819,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510513</v>
+        <v>510522</v>
       </c>
       <c r="R3" t="n">
-        <v>7001652</v>
+        <v>7001662</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,6 +897,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -905,10 +938,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121098323</v>
+        <v>121097284</v>
       </c>
       <c r="B4" t="n">
-        <v>74708</v>
+        <v>57504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,34 +954,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510503</v>
+        <v>510508</v>
       </c>
       <c r="R4" t="n">
-        <v>7001630</v>
+        <v>7001663</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,10 +1049,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121097307</v>
+        <v>121098323</v>
       </c>
       <c r="B5" t="n">
-        <v>57351</v>
+        <v>74710</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,42 +1065,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>510514</v>
+        <v>510503</v>
       </c>
       <c r="R5" t="n">
-        <v>7001648</v>
+        <v>7001630</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,31 +1135,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1142,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121097263</v>
+        <v>121098265</v>
       </c>
       <c r="B6" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1182,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510522</v>
+        <v>510510</v>
       </c>
       <c r="R6" t="n">
-        <v>7001662</v>
+        <v>7001653</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121097256</v>
+        <v>121097354</v>
       </c>
       <c r="B7" t="n">
-        <v>57351</v>
+        <v>90727</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,42 +1269,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510522</v>
+        <v>510507</v>
       </c>
       <c r="R7" t="n">
-        <v>7001662</v>
+        <v>7001641</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,31 +1339,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1379,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121098265</v>
+        <v>121097307</v>
       </c>
       <c r="B8" t="n">
-        <v>79682</v>
+        <v>57351</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1395,34 +1371,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510510</v>
+        <v>510514</v>
       </c>
       <c r="R8" t="n">
-        <v>7001653</v>
+        <v>7001648</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1465,6 +1449,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1481,10 +1490,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121097284</v>
+        <v>121098199</v>
       </c>
       <c r="B9" t="n">
-        <v>57504</v>
+        <v>90995</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1497,43 +1506,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510508</v>
+        <v>510513</v>
       </c>
       <c r="R9" t="n">
-        <v>7001663</v>
+        <v>7001652</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1592,10 +1592,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121097354</v>
+        <v>121097263</v>
       </c>
       <c r="B10" t="n">
-        <v>90715</v>
+        <v>79685</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,21 +1608,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510507</v>
+        <v>510522</v>
       </c>
       <c r="R10" t="n">
-        <v>7001641</v>
+        <v>7001662</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1697,7 +1697,7 @@
         <v>121099202</v>
       </c>
       <c r="B11" t="n">
-        <v>78337</v>
+        <v>78340</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1796,10 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121098269</v>
+        <v>121156706</v>
       </c>
       <c r="B12" t="n">
-        <v>79718</v>
+        <v>90709</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1808,45 +1808,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillmyren, Lillmyren, Jmt</t>
+          <t>Porten, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510487</v>
+        <v>510388</v>
       </c>
       <c r="R12" t="n">
-        <v>7001652</v>
+        <v>7001745</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1898,22 +1894,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1931,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121156706</v>
+        <v>121098825</v>
       </c>
       <c r="B13" t="n">
-        <v>90697</v>
+        <v>91397</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,34 +1939,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Porten, Jmt</t>
+          <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
@@ -2044,7 +2048,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Både med och utan markkontakt. Delen av stammen där sprickporingens fruktkroppar växer ligger ca 2 dm över marken. # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2062,10 +2066,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121098825</v>
+        <v>121156704</v>
       </c>
       <c r="B14" t="n">
-        <v>91385</v>
+        <v>98094</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2078,45 +2082,54 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>67</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>170</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Porten, Porten, Jmt</t>
+          <t>Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510388</v>
+        <v>510486</v>
       </c>
       <c r="R14" t="n">
-        <v>7001745</v>
+        <v>7001664</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2151,6 +2164,11 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Minst 170 st. skott/stjälkar och 6 st. fröställningar av knärot inom ca 1 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2166,24 +2184,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Både med och utan markkontakt. Delen av stammen där sprickporingens fruktkroppar växer ligger ca 2 dm över marken. # Picea abies</t>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2201,10 +2204,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121156704</v>
+        <v>121097723</v>
       </c>
       <c r="B15" t="n">
-        <v>98081</v>
+        <v>95641</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2213,58 +2216,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lillmyren, Jmt</t>
+          <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510486</v>
+        <v>510506</v>
       </c>
       <c r="R15" t="n">
-        <v>7001664</v>
+        <v>7001644</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2299,11 +2286,6 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Minst 170 st. skott/stjälkar och 6 st. fröställningar av knärot inom ca 1 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2317,11 +2299,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2339,10 +2316,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121156685</v>
+        <v>121156694</v>
       </c>
       <c r="B16" t="n">
-        <v>57367</v>
+        <v>57351</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2355,16 +2332,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2377,7 +2354,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2427,11 +2404,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska hackspår av spillkråka i basen av en levande granstam och i en kolad stubbe.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2483,10 +2455,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121099463</v>
+        <v>121156685</v>
       </c>
       <c r="B17" t="n">
-        <v>79711</v>
+        <v>57367</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2495,48 +2467,53 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Porten, Porten, Jmt</t>
+          <t>Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510317</v>
+        <v>510480</v>
       </c>
       <c r="R17" t="n">
-        <v>7001784</v>
+        <v>7001661</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2568,13 +2545,17 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska hackspår av spillkråka i basen av en levande granstam och i en kolad stubbe.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2585,22 +2566,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2618,10 +2599,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121156694</v>
+        <v>121098269</v>
       </c>
       <c r="B18" t="n">
-        <v>57351</v>
+        <v>79721</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2630,53 +2611,48 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lillmyren, Jmt</t>
+          <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>510480</v>
+        <v>510487</v>
       </c>
       <c r="R18" t="n">
-        <v>7001661</v>
+        <v>7001652</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2714,6 +2690,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2724,22 +2701,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2760,7 +2737,7 @@
         <v>121099320</v>
       </c>
       <c r="B19" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2892,10 +2869,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121097723</v>
+        <v>121099463</v>
       </c>
       <c r="B20" t="n">
-        <v>95628</v>
+        <v>79714</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2904,42 +2881,45 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lillmyren, Lillmyren, Jmt</t>
+          <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>510506</v>
+        <v>510317</v>
       </c>
       <c r="R20" t="n">
-        <v>7001644</v>
+        <v>7001784</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2987,6 +2967,26 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3004,10 +3004,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121098578</v>
+        <v>121098790</v>
       </c>
       <c r="B21" t="n">
-        <v>95628</v>
+        <v>95641</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>510428</v>
+        <v>510395</v>
       </c>
       <c r="R21" t="n">
-        <v>7001712</v>
+        <v>7001752</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -3126,10 +3126,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121099891</v>
+        <v>121098783</v>
       </c>
       <c r="B22" t="n">
-        <v>79683</v>
+        <v>90995</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3142,21 +3142,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>510301</v>
+        <v>510388</v>
       </c>
       <c r="R22" t="n">
-        <v>7001726</v>
+        <v>7001741</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3219,22 +3219,27 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3252,10 +3257,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121099111</v>
+        <v>121099190</v>
       </c>
       <c r="B23" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3287,7 +3292,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3312,10 +3317,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>510355</v>
+        <v>510363</v>
       </c>
       <c r="R23" t="n">
-        <v>7001742</v>
+        <v>7001774</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3380,10 +3385,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121098783</v>
+        <v>121098983</v>
       </c>
       <c r="B24" t="n">
-        <v>90983</v>
+        <v>90723</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3396,21 +3401,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3423,7 +3428,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>510388</v>
+        <v>510387</v>
       </c>
       <c r="R24" t="n">
         <v>7001741</v>
@@ -3473,17 +3478,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
@@ -3493,7 +3488,7 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3511,10 +3506,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121099162</v>
+        <v>121099213</v>
       </c>
       <c r="B25" t="n">
-        <v>57504</v>
+        <v>78604</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3527,50 +3522,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>510354</v>
+        <v>510360</v>
       </c>
       <c r="R25" t="n">
-        <v>7001746</v>
+        <v>7001779</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3611,6 +3593,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3634,10 +3617,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121099210</v>
+        <v>121099111</v>
       </c>
       <c r="B26" t="n">
-        <v>90662</v>
+        <v>98094</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3646,41 +3629,58 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>510364</v>
+        <v>510355</v>
       </c>
       <c r="R26" t="n">
-        <v>7001767</v>
+        <v>7001742</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121099277</v>
+        <v>121099891</v>
       </c>
       <c r="B27" t="n">
-        <v>74708</v>
+        <v>79686</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3761,21 +3761,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>510345</v>
+        <v>510301</v>
       </c>
       <c r="R27" t="n">
-        <v>7001762</v>
+        <v>7001726</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3843,17 +3843,17 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3871,10 +3871,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121098983</v>
+        <v>121099241</v>
       </c>
       <c r="B28" t="n">
-        <v>90711</v>
+        <v>78604</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3887,21 +3887,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>510387</v>
+        <v>510337</v>
       </c>
       <c r="R28" t="n">
-        <v>7001741</v>
+        <v>7001780</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3965,16 +3965,6 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3992,10 +3982,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121098790</v>
+        <v>121099210</v>
       </c>
       <c r="B29" t="n">
-        <v>95628</v>
+        <v>90674</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4004,31 +3994,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4036,10 +4025,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>510395</v>
+        <v>510364</v>
       </c>
       <c r="R29" t="n">
-        <v>7001752</v>
+        <v>7001767</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4086,17 +4075,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4114,10 +4093,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121099190</v>
+        <v>121099277</v>
       </c>
       <c r="B30" t="n">
-        <v>98081</v>
+        <v>74710</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4126,58 +4105,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>510363</v>
+        <v>510345</v>
       </c>
       <c r="R30" t="n">
-        <v>7001774</v>
+        <v>7001762</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4225,6 +4187,21 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4245,7 +4222,7 @@
         <v>121099090</v>
       </c>
       <c r="B31" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4370,10 +4347,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121099241</v>
+        <v>121098578</v>
       </c>
       <c r="B32" t="n">
-        <v>78601</v>
+        <v>95641</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4386,26 +4363,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4413,10 +4391,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>510337</v>
+        <v>510428</v>
       </c>
       <c r="R32" t="n">
-        <v>7001780</v>
+        <v>7001712</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4464,6 +4442,16 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4481,10 +4469,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121099213</v>
+        <v>121099162</v>
       </c>
       <c r="B33" t="n">
-        <v>78601</v>
+        <v>57504</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4497,37 +4485,50 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>510360</v>
+        <v>510354</v>
       </c>
       <c r="R33" t="n">
-        <v>7001779</v>
+        <v>7001746</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4568,7 +4569,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 50126-2024 artfynd.xlsx
+++ b/artfynd/A 50126-2024 artfynd.xlsx
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121097256</v>
+        <v>121098265</v>
       </c>
       <c r="B3" t="n">
-        <v>57351</v>
+        <v>79685</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,42 +819,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510522</v>
+        <v>510510</v>
       </c>
       <c r="R3" t="n">
-        <v>7001662</v>
+        <v>7001653</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,31 +889,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -938,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121097284</v>
+        <v>121097354</v>
       </c>
       <c r="B4" t="n">
-        <v>57504</v>
+        <v>90728</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,43 +921,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510508</v>
+        <v>510507</v>
       </c>
       <c r="R4" t="n">
-        <v>7001663</v>
+        <v>7001641</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1049,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121098323</v>
+        <v>121097284</v>
       </c>
       <c r="B5" t="n">
-        <v>74710</v>
+        <v>57504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1065,34 +1023,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>510503</v>
+        <v>510508</v>
       </c>
       <c r="R5" t="n">
-        <v>7001630</v>
+        <v>7001663</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1151,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121098265</v>
+        <v>121098199</v>
       </c>
       <c r="B6" t="n">
-        <v>79685</v>
+        <v>90996</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,21 +1134,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1191,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510510</v>
+        <v>510513</v>
       </c>
       <c r="R6" t="n">
-        <v>7001653</v>
+        <v>7001652</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1253,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121097354</v>
+        <v>121098323</v>
       </c>
       <c r="B7" t="n">
-        <v>90727</v>
+        <v>74710</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,21 +1236,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1293,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510507</v>
+        <v>510503</v>
       </c>
       <c r="R7" t="n">
-        <v>7001641</v>
+        <v>7001630</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1490,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121098199</v>
+        <v>121097256</v>
       </c>
       <c r="B9" t="n">
-        <v>90995</v>
+        <v>57351</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,34 +1473,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510513</v>
+        <v>510522</v>
       </c>
       <c r="R9" t="n">
-        <v>7001652</v>
+        <v>7001662</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1576,6 +1551,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1796,10 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121156706</v>
+        <v>121097723</v>
       </c>
       <c r="B12" t="n">
-        <v>90709</v>
+        <v>95642</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1812,37 +1812,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Porten, Jmt</t>
+          <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510388</v>
+        <v>510506</v>
       </c>
       <c r="R12" t="n">
-        <v>7001745</v>
+        <v>7001644</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1890,26 +1891,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1927,10 +1908,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121098825</v>
+        <v>121156704</v>
       </c>
       <c r="B13" t="n">
-        <v>91397</v>
+        <v>98095</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,45 +1924,54 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>67</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>170</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Porten, Porten, Jmt</t>
+          <t>Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510388</v>
+        <v>510486</v>
       </c>
       <c r="R13" t="n">
-        <v>7001745</v>
+        <v>7001664</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2016,6 +2006,11 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Minst 170 st. skott/stjälkar och 6 st. fröställningar av knärot inom ca 1 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2031,24 +2026,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Både med och utan markkontakt. Delen av stammen där sprickporingens fruktkroppar växer ligger ca 2 dm över marken. # Picea abies</t>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2066,10 +2046,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121156704</v>
+        <v>121156706</v>
       </c>
       <c r="B14" t="n">
-        <v>98094</v>
+        <v>90710</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2078,58 +2058,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lillmyren, Jmt</t>
+          <t>Porten, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510486</v>
+        <v>510388</v>
       </c>
       <c r="R14" t="n">
-        <v>7001664</v>
+        <v>7001745</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2164,11 +2127,6 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Minst 170 st. skott/stjälkar och 6 st. fröställningar av knärot inom ca 1 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2184,9 +2142,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>På frisk och frisk-fuktig mark.</t>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2204,10 +2177,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121097723</v>
+        <v>121156694</v>
       </c>
       <c r="B15" t="n">
-        <v>95641</v>
+        <v>57351</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2220,41 +2193,49 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lillmyren, Lillmyren, Jmt</t>
+          <t>Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510506</v>
+        <v>510480</v>
       </c>
       <c r="R15" t="n">
-        <v>7001644</v>
+        <v>7001661</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2292,13 +2273,32 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2316,10 +2316,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121156694</v>
+        <v>121098825</v>
       </c>
       <c r="B16" t="n">
-        <v>57351</v>
+        <v>91398</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2328,53 +2328,52 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lillmyren, Jmt</t>
+          <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510480</v>
+        <v>510388</v>
       </c>
       <c r="R16" t="n">
-        <v>7001661</v>
+        <v>7001745</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2412,6 +2411,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2432,12 +2432,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Både med och utan markkontakt. Delen av stammen där sprickporingens fruktkroppar växer ligger ca 2 dm över marken. # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2455,10 +2455,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121156685</v>
+        <v>121099320</v>
       </c>
       <c r="B17" t="n">
-        <v>57367</v>
+        <v>79685</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2471,49 +2471,44 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lillmyren, Jmt</t>
+          <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510480</v>
+        <v>510339</v>
       </c>
       <c r="R17" t="n">
-        <v>7001661</v>
+        <v>7001763</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2545,17 +2540,13 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska hackspår av spillkråka i basen av en levande granstam och i en kolad stubbe.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2566,22 +2557,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2599,10 +2590,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121098269</v>
+        <v>121099463</v>
       </c>
       <c r="B18" t="n">
-        <v>79721</v>
+        <v>79714</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2615,21 +2606,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2642,14 +2633,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lillmyren, Lillmyren, Jmt</t>
+          <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>510487</v>
+        <v>510317</v>
       </c>
       <c r="R18" t="n">
-        <v>7001652</v>
+        <v>7001784</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2734,10 +2725,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121099320</v>
+        <v>121098269</v>
       </c>
       <c r="B19" t="n">
-        <v>79685</v>
+        <v>79721</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2746,45 +2737,45 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Porten, Porten, Jmt</t>
+          <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>510339</v>
+        <v>510487</v>
       </c>
       <c r="R19" t="n">
-        <v>7001763</v>
+        <v>7001652</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2869,10 +2860,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121099463</v>
+        <v>121156685</v>
       </c>
       <c r="B20" t="n">
-        <v>79714</v>
+        <v>57367</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2881,48 +2872,53 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Porten, Porten, Jmt</t>
+          <t>Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>510317</v>
+        <v>510480</v>
       </c>
       <c r="R20" t="n">
-        <v>7001784</v>
+        <v>7001661</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2954,13 +2950,17 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska hackspår av spillkråka i basen av en levande granstam och i en kolad stubbe.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2971,22 +2971,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3004,10 +3004,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121098790</v>
+        <v>121099277</v>
       </c>
       <c r="B21" t="n">
-        <v>95641</v>
+        <v>74710</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3020,27 +3020,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3048,10 +3047,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>510395</v>
+        <v>510345</v>
       </c>
       <c r="R21" t="n">
-        <v>7001752</v>
+        <v>7001762</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3098,17 +3097,22 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3126,10 +3130,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121098783</v>
+        <v>121099190</v>
       </c>
       <c r="B22" t="n">
-        <v>90995</v>
+        <v>98095</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3138,41 +3142,58 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>510388</v>
+        <v>510363</v>
       </c>
       <c r="R22" t="n">
-        <v>7001741</v>
+        <v>7001774</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3219,27 +3240,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3257,10 +3258,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121099190</v>
+        <v>121099213</v>
       </c>
       <c r="B23" t="n">
-        <v>98094</v>
+        <v>78604</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3269,58 +3270,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>510363</v>
+        <v>510360</v>
       </c>
       <c r="R23" t="n">
-        <v>7001774</v>
+        <v>7001779</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3385,10 +3369,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121098983</v>
+        <v>121099210</v>
       </c>
       <c r="B24" t="n">
-        <v>90723</v>
+        <v>90675</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3397,25 +3381,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3428,10 +3412,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>510387</v>
+        <v>510364</v>
       </c>
       <c r="R24" t="n">
-        <v>7001741</v>
+        <v>7001767</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3479,16 +3463,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3506,10 +3480,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121099213</v>
+        <v>121098578</v>
       </c>
       <c r="B25" t="n">
-        <v>78604</v>
+        <v>95642</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3522,26 +3496,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3549,10 +3524,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>510360</v>
+        <v>510428</v>
       </c>
       <c r="R25" t="n">
-        <v>7001779</v>
+        <v>7001712</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3600,6 +3575,16 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3617,10 +3602,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121099111</v>
+        <v>121099090</v>
       </c>
       <c r="B26" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3652,7 +3637,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3677,10 +3662,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>510355</v>
+        <v>510375</v>
       </c>
       <c r="R26" t="n">
-        <v>7001742</v>
+        <v>7001739</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3745,10 +3730,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121099891</v>
+        <v>121099111</v>
       </c>
       <c r="B27" t="n">
-        <v>79686</v>
+        <v>98095</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3757,41 +3742,58 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>510301</v>
+        <v>510355</v>
       </c>
       <c r="R27" t="n">
-        <v>7001726</v>
+        <v>7001742</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3839,21 +3841,6 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3871,10 +3858,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121099241</v>
+        <v>121099891</v>
       </c>
       <c r="B28" t="n">
-        <v>78604</v>
+        <v>79686</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3887,21 +3874,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3914,10 +3901,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>510337</v>
+        <v>510301</v>
       </c>
       <c r="R28" t="n">
-        <v>7001780</v>
+        <v>7001726</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3965,6 +3952,21 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3982,10 +3984,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121099210</v>
+        <v>121098790</v>
       </c>
       <c r="B29" t="n">
-        <v>90674</v>
+        <v>95642</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3994,30 +3996,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4025,10 +4028,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>510364</v>
+        <v>510395</v>
       </c>
       <c r="R29" t="n">
-        <v>7001767</v>
+        <v>7001752</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4075,7 +4078,17 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4093,10 +4106,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121099277</v>
+        <v>121099162</v>
       </c>
       <c r="B30" t="n">
-        <v>74710</v>
+        <v>57504</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4109,37 +4122,50 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>510345</v>
+        <v>510354</v>
       </c>
       <c r="R30" t="n">
-        <v>7001762</v>
+        <v>7001746</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4180,28 +4206,12 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4219,10 +4229,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121099090</v>
+        <v>121098983</v>
       </c>
       <c r="B31" t="n">
-        <v>98094</v>
+        <v>90724</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4231,58 +4241,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>510375</v>
+        <v>510387</v>
       </c>
       <c r="R31" t="n">
-        <v>7001739</v>
+        <v>7001741</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4330,6 +4323,16 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4347,10 +4350,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121098578</v>
+        <v>121098783</v>
       </c>
       <c r="B32" t="n">
-        <v>95641</v>
+        <v>90996</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4363,27 +4366,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4391,10 +4393,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>510428</v>
+        <v>510388</v>
       </c>
       <c r="R32" t="n">
-        <v>7001712</v>
+        <v>7001741</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4441,7 +4443,17 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
@@ -4451,7 +4463,7 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4469,10 +4481,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121099162</v>
+        <v>121099241</v>
       </c>
       <c r="B33" t="n">
-        <v>57504</v>
+        <v>78604</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4485,50 +4497,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>510354</v>
+        <v>510337</v>
       </c>
       <c r="R33" t="n">
-        <v>7001746</v>
+        <v>7001780</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4569,6 +4568,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 50126-2024 artfynd.xlsx
+++ b/artfynd/A 50126-2024 artfynd.xlsx
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121098265</v>
+        <v>121097263</v>
       </c>
       <c r="B3" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510510</v>
+        <v>510522</v>
       </c>
       <c r="R3" t="n">
-        <v>7001653</v>
+        <v>7001662</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121097354</v>
+        <v>121097256</v>
       </c>
       <c r="B4" t="n">
-        <v>90728</v>
+        <v>57354</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,34 +921,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510507</v>
+        <v>510522</v>
       </c>
       <c r="R4" t="n">
-        <v>7001641</v>
+        <v>7001662</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,6 +999,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1007,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121097284</v>
+        <v>121097307</v>
       </c>
       <c r="B5" t="n">
-        <v>57504</v>
+        <v>57354</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,43 +1056,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>510508</v>
+        <v>510514</v>
       </c>
       <c r="R5" t="n">
-        <v>7001663</v>
+        <v>7001648</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,6 +1134,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1118,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121098199</v>
+        <v>121097354</v>
       </c>
       <c r="B6" t="n">
-        <v>90996</v>
+        <v>90731</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,21 +1191,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1215,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510513</v>
+        <v>510507</v>
       </c>
       <c r="R6" t="n">
-        <v>7001652</v>
+        <v>7001641</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1280,7 @@
         <v>121098323</v>
       </c>
       <c r="B7" t="n">
-        <v>74710</v>
+        <v>74713</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1322,10 +1379,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121097307</v>
+        <v>121098199</v>
       </c>
       <c r="B8" t="n">
-        <v>57351</v>
+        <v>90999</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,42 +1395,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510514</v>
+        <v>510513</v>
       </c>
       <c r="R8" t="n">
-        <v>7001648</v>
+        <v>7001652</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,31 +1465,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1457,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121097256</v>
+        <v>121098265</v>
       </c>
       <c r="B9" t="n">
-        <v>57351</v>
+        <v>79688</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,42 +1497,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510522</v>
+        <v>510510</v>
       </c>
       <c r="R9" t="n">
-        <v>7001662</v>
+        <v>7001653</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,31 +1567,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1592,10 +1583,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121097263</v>
+        <v>121097284</v>
       </c>
       <c r="B10" t="n">
-        <v>79685</v>
+        <v>57507</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,34 +1599,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510522</v>
+        <v>510508</v>
       </c>
       <c r="R10" t="n">
-        <v>7001662</v>
+        <v>7001663</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1697,7 +1697,7 @@
         <v>121099202</v>
       </c>
       <c r="B11" t="n">
-        <v>78340</v>
+        <v>78343</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1796,10 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121097723</v>
+        <v>121156694</v>
       </c>
       <c r="B12" t="n">
-        <v>95642</v>
+        <v>57354</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1812,41 +1812,49 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillmyren, Lillmyren, Jmt</t>
+          <t>Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510506</v>
+        <v>510480</v>
       </c>
       <c r="R12" t="n">
-        <v>7001644</v>
+        <v>7001661</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1884,13 +1892,32 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1908,10 +1935,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121156704</v>
+        <v>121097723</v>
       </c>
       <c r="B13" t="n">
-        <v>98095</v>
+        <v>95645</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1920,58 +1947,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lillmyren, Jmt</t>
+          <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510486</v>
+        <v>510506</v>
       </c>
       <c r="R13" t="n">
-        <v>7001664</v>
+        <v>7001644</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2006,11 +2017,6 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Minst 170 st. skott/stjälkar och 6 st. fröställningar av knärot inom ca 1 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2024,11 +2030,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2046,10 +2047,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121156706</v>
+        <v>121099463</v>
       </c>
       <c r="B14" t="n">
-        <v>90710</v>
+        <v>79717</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2058,41 +2059,45 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Porten, Jmt</t>
+          <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510388</v>
+        <v>510317</v>
       </c>
       <c r="R14" t="n">
-        <v>7001745</v>
+        <v>7001784</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2144,22 +2149,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2177,10 +2182,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121156694</v>
+        <v>121156704</v>
       </c>
       <c r="B15" t="n">
-        <v>57351</v>
+        <v>98098</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2189,35 +2194,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2229,13 +2242,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510480</v>
+        <v>510486</v>
       </c>
       <c r="R15" t="n">
-        <v>7001661</v>
+        <v>7001664</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2267,12 +2280,18 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Minst 170 st. skott/stjälkar och 6 st. fröställningar av knärot inom ca 1 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2281,24 +2300,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2316,10 +2320,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121098825</v>
+        <v>121099320</v>
       </c>
       <c r="B16" t="n">
-        <v>91398</v>
+        <v>79688</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2328,38 +2332,34 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>67</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510388</v>
+        <v>510339</v>
       </c>
       <c r="R16" t="n">
-        <v>7001745</v>
+        <v>7001763</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2422,22 +2422,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Både med och utan markkontakt. Delen av stammen där sprickporingens fruktkroppar växer ligger ca 2 dm över marken. # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2455,10 +2455,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121099320</v>
+        <v>121098269</v>
       </c>
       <c r="B17" t="n">
-        <v>79685</v>
+        <v>79724</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2467,45 +2467,45 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Porten, Porten, Jmt</t>
+          <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510339</v>
+        <v>510487</v>
       </c>
       <c r="R17" t="n">
-        <v>7001763</v>
+        <v>7001652</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2590,10 +2590,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121099463</v>
+        <v>121156706</v>
       </c>
       <c r="B18" t="n">
-        <v>79714</v>
+        <v>90713</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2602,45 +2602,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Porten, Porten, Jmt</t>
+          <t>Porten, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>510317</v>
+        <v>510388</v>
       </c>
       <c r="R18" t="n">
-        <v>7001784</v>
+        <v>7001745</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2692,22 +2688,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2725,10 +2721,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121098269</v>
+        <v>121156685</v>
       </c>
       <c r="B19" t="n">
-        <v>79721</v>
+        <v>57370</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2737,48 +2733,53 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lillmyren, Lillmyren, Jmt</t>
+          <t>Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>510487</v>
+        <v>510480</v>
       </c>
       <c r="R19" t="n">
-        <v>7001652</v>
+        <v>7001661</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2810,13 +2811,17 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska hackspår av spillkråka i basen av en levande granstam och i en kolad stubbe.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2827,22 +2832,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2860,10 +2865,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121156685</v>
+        <v>121098825</v>
       </c>
       <c r="B20" t="n">
-        <v>57367</v>
+        <v>91401</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2872,53 +2877,52 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>67</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lillmyren, Jmt</t>
+          <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>510480</v>
+        <v>510388</v>
       </c>
       <c r="R20" t="n">
-        <v>7001661</v>
+        <v>7001745</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2950,17 +2954,13 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska hackspår av spillkråka i basen av en levande granstam och i en kolad stubbe.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2981,12 +2981,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Både med och utan markkontakt. Delen av stammen där sprickporingens fruktkroppar växer ligger ca 2 dm över marken. # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3004,10 +3004,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121099277</v>
+        <v>121099190</v>
       </c>
       <c r="B21" t="n">
-        <v>74710</v>
+        <v>98098</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3016,41 +3016,58 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>510345</v>
+        <v>510363</v>
       </c>
       <c r="R21" t="n">
-        <v>7001762</v>
+        <v>7001774</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3098,21 +3115,6 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3130,10 +3132,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121099190</v>
+        <v>121099277</v>
       </c>
       <c r="B22" t="n">
-        <v>98095</v>
+        <v>74713</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3142,58 +3144,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>510363</v>
+        <v>510345</v>
       </c>
       <c r="R22" t="n">
-        <v>7001774</v>
+        <v>7001762</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3241,6 +3226,21 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3258,10 +3258,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121099213</v>
+        <v>121099111</v>
       </c>
       <c r="B23" t="n">
-        <v>78604</v>
+        <v>98098</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3270,41 +3270,58 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>510360</v>
+        <v>510355</v>
       </c>
       <c r="R23" t="n">
-        <v>7001779</v>
+        <v>7001742</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3369,10 +3386,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121099210</v>
+        <v>121098783</v>
       </c>
       <c r="B24" t="n">
-        <v>90675</v>
+        <v>90999</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3381,25 +3398,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3412,10 +3429,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>510364</v>
+        <v>510388</v>
       </c>
       <c r="R24" t="n">
-        <v>7001767</v>
+        <v>7001741</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3462,7 +3479,27 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3480,10 +3517,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121098578</v>
+        <v>121099213</v>
       </c>
       <c r="B25" t="n">
-        <v>95642</v>
+        <v>78607</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3496,27 +3533,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3524,10 +3560,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>510428</v>
+        <v>510360</v>
       </c>
       <c r="R25" t="n">
-        <v>7001712</v>
+        <v>7001779</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3575,16 +3611,6 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3602,10 +3628,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121099090</v>
+        <v>121098578</v>
       </c>
       <c r="B26" t="n">
-        <v>98095</v>
+        <v>95645</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3614,58 +3640,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>510375</v>
+        <v>510428</v>
       </c>
       <c r="R26" t="n">
-        <v>7001739</v>
+        <v>7001712</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3713,6 +3723,16 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3730,10 +3750,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121099111</v>
+        <v>121099210</v>
       </c>
       <c r="B27" t="n">
-        <v>98095</v>
+        <v>90678</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3742,58 +3762,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>510355</v>
+        <v>510364</v>
       </c>
       <c r="R27" t="n">
-        <v>7001742</v>
+        <v>7001767</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3858,10 +3861,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121099891</v>
+        <v>121098983</v>
       </c>
       <c r="B28" t="n">
-        <v>79686</v>
+        <v>90727</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3874,21 +3877,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3901,10 +3904,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>510301</v>
+        <v>510387</v>
       </c>
       <c r="R28" t="n">
-        <v>7001726</v>
+        <v>7001741</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3954,19 +3957,14 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3984,10 +3982,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121098790</v>
+        <v>121099090</v>
       </c>
       <c r="B29" t="n">
-        <v>95642</v>
+        <v>98098</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3996,42 +3994,58 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>510395</v>
+        <v>510375</v>
       </c>
       <c r="R29" t="n">
-        <v>7001752</v>
+        <v>7001739</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4078,17 +4092,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4106,10 +4110,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121099162</v>
+        <v>121099891</v>
       </c>
       <c r="B30" t="n">
-        <v>57504</v>
+        <v>79689</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4122,50 +4126,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>510354</v>
+        <v>510301</v>
       </c>
       <c r="R30" t="n">
-        <v>7001746</v>
+        <v>7001726</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4206,12 +4197,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4229,10 +4236,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121098983</v>
+        <v>121099162</v>
       </c>
       <c r="B31" t="n">
-        <v>90724</v>
+        <v>57507</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4245,37 +4252,50 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>510387</v>
+        <v>510354</v>
       </c>
       <c r="R31" t="n">
-        <v>7001741</v>
+        <v>7001746</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4316,23 +4336,12 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4350,10 +4359,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121098783</v>
+        <v>121099241</v>
       </c>
       <c r="B32" t="n">
-        <v>90996</v>
+        <v>78607</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4366,21 +4375,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4393,10 +4402,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>510388</v>
+        <v>510337</v>
       </c>
       <c r="R32" t="n">
-        <v>7001741</v>
+        <v>7001780</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4443,27 +4452,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4481,10 +4470,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121099241</v>
+        <v>121098790</v>
       </c>
       <c r="B33" t="n">
-        <v>78604</v>
+        <v>95645</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4497,26 +4486,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4524,10 +4514,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>510337</v>
+        <v>510395</v>
       </c>
       <c r="R33" t="n">
-        <v>7001780</v>
+        <v>7001752</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4574,7 +4564,17 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>

--- a/artfynd/A 50126-2024 artfynd.xlsx
+++ b/artfynd/A 50126-2024 artfynd.xlsx
@@ -1796,10 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121156694</v>
+        <v>121098825</v>
       </c>
       <c r="B12" t="n">
-        <v>57354</v>
+        <v>91401</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1808,53 +1808,52 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillmyren, Jmt</t>
+          <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510480</v>
+        <v>510388</v>
       </c>
       <c r="R12" t="n">
-        <v>7001661</v>
+        <v>7001745</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1892,6 +1891,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1912,12 +1912,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Både med och utan markkontakt. Delen av stammen där sprickporingens fruktkroppar växer ligger ca 2 dm över marken. # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1935,10 +1935,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121097723</v>
+        <v>121156694</v>
       </c>
       <c r="B13" t="n">
-        <v>95645</v>
+        <v>57354</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1951,41 +1951,49 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lillmyren, Lillmyren, Jmt</t>
+          <t>Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510506</v>
+        <v>510480</v>
       </c>
       <c r="R13" t="n">
-        <v>7001644</v>
+        <v>7001661</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2023,13 +2031,32 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2047,10 +2074,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121099463</v>
+        <v>121098269</v>
       </c>
       <c r="B14" t="n">
-        <v>79717</v>
+        <v>79724</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2063,21 +2090,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2090,14 +2117,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Porten, Porten, Jmt</t>
+          <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510317</v>
+        <v>510487</v>
       </c>
       <c r="R14" t="n">
-        <v>7001784</v>
+        <v>7001652</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2182,10 +2209,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121156704</v>
+        <v>121156685</v>
       </c>
       <c r="B15" t="n">
-        <v>98098</v>
+        <v>57370</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2194,43 +2221,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2242,13 +2261,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510486</v>
+        <v>510480</v>
       </c>
       <c r="R15" t="n">
-        <v>7001664</v>
+        <v>7001661</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2282,7 +2301,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Minst 170 st. skott/stjälkar och 6 st. fröställningar av knärot inom ca 1 m2 yta.</t>
+          <t>Färska hackspår av spillkråka i basen av en levande granstam och i en kolad stubbe.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,7 +2310,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2300,9 +2318,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>På frisk och frisk-fuktig mark.</t>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2320,10 +2353,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121099320</v>
+        <v>121156706</v>
       </c>
       <c r="B16" t="n">
-        <v>79688</v>
+        <v>90713</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2336,41 +2369,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Porten, Porten, Jmt</t>
+          <t>Porten, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510339</v>
+        <v>510388</v>
       </c>
       <c r="R16" t="n">
-        <v>7001763</v>
+        <v>7001745</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2422,22 +2451,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2455,10 +2484,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121098269</v>
+        <v>121156704</v>
       </c>
       <c r="B17" t="n">
-        <v>79724</v>
+        <v>98098</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2467,45 +2496,58 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lillmyren, Lillmyren, Jmt</t>
+          <t>Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510487</v>
+        <v>510486</v>
       </c>
       <c r="R17" t="n">
-        <v>7001652</v>
+        <v>7001664</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2540,6 +2582,11 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Minst 170 st. skott/stjälkar och 6 st. fröställningar av knärot inom ca 1 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2555,24 +2602,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2590,10 +2622,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121156706</v>
+        <v>121097723</v>
       </c>
       <c r="B18" t="n">
-        <v>90713</v>
+        <v>95645</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2606,37 +2638,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Porten, Jmt</t>
+          <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>510388</v>
+        <v>510506</v>
       </c>
       <c r="R18" t="n">
-        <v>7001745</v>
+        <v>7001644</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2684,26 +2717,6 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2721,10 +2734,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121156685</v>
+        <v>121099320</v>
       </c>
       <c r="B19" t="n">
-        <v>57370</v>
+        <v>79688</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2737,49 +2750,44 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lillmyren, Jmt</t>
+          <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>510480</v>
+        <v>510339</v>
       </c>
       <c r="R19" t="n">
-        <v>7001661</v>
+        <v>7001763</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2811,17 +2819,13 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska hackspår av spillkråka i basen av en levande granstam och i en kolad stubbe.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2832,22 +2836,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2865,10 +2869,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121098825</v>
+        <v>121099463</v>
       </c>
       <c r="B20" t="n">
-        <v>91401</v>
+        <v>79717</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2877,38 +2881,34 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>67</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>510388</v>
+        <v>510317</v>
       </c>
       <c r="R20" t="n">
-        <v>7001745</v>
+        <v>7001784</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2971,22 +2971,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Både med och utan markkontakt. Delen av stammen där sprickporingens fruktkroppar växer ligger ca 2 dm över marken. # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3004,10 +3004,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121099190</v>
+        <v>121099241</v>
       </c>
       <c r="B21" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3016,58 +3016,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>510363</v>
+        <v>510337</v>
       </c>
       <c r="R21" t="n">
-        <v>7001774</v>
+        <v>7001780</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3132,10 +3115,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121099277</v>
+        <v>121098578</v>
       </c>
       <c r="B22" t="n">
-        <v>74713</v>
+        <v>95645</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3148,26 +3131,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3175,10 +3159,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>510345</v>
+        <v>510428</v>
       </c>
       <c r="R22" t="n">
-        <v>7001762</v>
+        <v>7001712</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3228,19 +3212,14 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3386,10 +3365,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121098783</v>
+        <v>121099213</v>
       </c>
       <c r="B24" t="n">
-        <v>90999</v>
+        <v>78607</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3402,21 +3381,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3429,10 +3408,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>510388</v>
+        <v>510360</v>
       </c>
       <c r="R24" t="n">
-        <v>7001741</v>
+        <v>7001779</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3479,27 +3458,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3517,10 +3476,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121099213</v>
+        <v>121098790</v>
       </c>
       <c r="B25" t="n">
-        <v>78607</v>
+        <v>95645</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3533,26 +3492,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3560,10 +3520,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>510360</v>
+        <v>510395</v>
       </c>
       <c r="R25" t="n">
-        <v>7001779</v>
+        <v>7001752</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3610,7 +3570,17 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3628,10 +3598,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121098578</v>
+        <v>121099090</v>
       </c>
       <c r="B26" t="n">
-        <v>95645</v>
+        <v>98098</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3640,42 +3610,58 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>510428</v>
+        <v>510375</v>
       </c>
       <c r="R26" t="n">
-        <v>7001712</v>
+        <v>7001739</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3723,16 +3709,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3750,10 +3726,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121099210</v>
+        <v>121099190</v>
       </c>
       <c r="B27" t="n">
-        <v>90678</v>
+        <v>98098</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3762,41 +3738,58 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>510364</v>
+        <v>510363</v>
       </c>
       <c r="R27" t="n">
-        <v>7001767</v>
+        <v>7001774</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3982,10 +3975,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121099090</v>
+        <v>121099891</v>
       </c>
       <c r="B29" t="n">
-        <v>98098</v>
+        <v>79689</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3994,58 +3987,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>510375</v>
+        <v>510301</v>
       </c>
       <c r="R29" t="n">
-        <v>7001739</v>
+        <v>7001726</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4093,6 +4069,21 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4110,10 +4101,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121099891</v>
+        <v>121098783</v>
       </c>
       <c r="B30" t="n">
-        <v>79689</v>
+        <v>90999</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4126,21 +4117,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4153,10 +4144,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>510301</v>
+        <v>510388</v>
       </c>
       <c r="R30" t="n">
-        <v>7001726</v>
+        <v>7001741</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4203,22 +4194,27 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4236,10 +4232,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121099162</v>
+        <v>121099210</v>
       </c>
       <c r="B31" t="n">
-        <v>57507</v>
+        <v>90678</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4248,54 +4244,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>510354</v>
+        <v>510364</v>
       </c>
       <c r="R31" t="n">
-        <v>7001746</v>
+        <v>7001767</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4336,6 +4319,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4359,10 +4343,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121099241</v>
+        <v>121099277</v>
       </c>
       <c r="B32" t="n">
-        <v>78607</v>
+        <v>74713</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4375,21 +4359,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4402,10 +4386,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>510337</v>
+        <v>510345</v>
       </c>
       <c r="R32" t="n">
-        <v>7001780</v>
+        <v>7001762</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4453,6 +4437,21 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4470,10 +4469,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121098790</v>
+        <v>121099162</v>
       </c>
       <c r="B33" t="n">
-        <v>95645</v>
+        <v>57507</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4486,38 +4485,50 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>510395</v>
+        <v>510354</v>
       </c>
       <c r="R33" t="n">
-        <v>7001752</v>
+        <v>7001746</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4558,23 +4569,12 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>

--- a/artfynd/A 50126-2024 artfynd.xlsx
+++ b/artfynd/A 50126-2024 artfynd.xlsx
@@ -3598,7 +3598,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121099090</v>
+        <v>121099190</v>
       </c>
       <c r="B26" t="n">
         <v>98098</v>
@@ -3633,7 +3633,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>510375</v>
+        <v>510363</v>
       </c>
       <c r="R26" t="n">
-        <v>7001739</v>
+        <v>7001774</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3726,7 +3726,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121099190</v>
+        <v>121099090</v>
       </c>
       <c r="B27" t="n">
         <v>98098</v>
@@ -3761,7 +3761,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3786,10 +3786,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>510363</v>
+        <v>510375</v>
       </c>
       <c r="R27" t="n">
-        <v>7001774</v>
+        <v>7001739</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 50126-2024 artfynd.xlsx
+++ b/artfynd/A 50126-2024 artfynd.xlsx
@@ -1796,10 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121098825</v>
+        <v>121156694</v>
       </c>
       <c r="B12" t="n">
-        <v>91401</v>
+        <v>57355</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1808,52 +1808,53 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Porten, Porten, Jmt</t>
+          <t>Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510388</v>
+        <v>510480</v>
       </c>
       <c r="R12" t="n">
-        <v>7001745</v>
+        <v>7001661</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1891,7 +1892,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1912,12 +1912,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Både med och utan markkontakt. Delen av stammen där sprickporingens fruktkroppar växer ligger ca 2 dm över marken. # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1935,10 +1935,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121156694</v>
+        <v>121156704</v>
       </c>
       <c r="B13" t="n">
-        <v>57354</v>
+        <v>98104</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,35 +1947,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1987,13 +1995,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510480</v>
+        <v>510486</v>
       </c>
       <c r="R13" t="n">
-        <v>7001661</v>
+        <v>7001664</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2025,12 +2033,18 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Minst 170 st. skott/stjälkar och 6 st. fröställningar av knärot inom ca 1 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2039,24 +2053,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2074,10 +2073,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121098269</v>
+        <v>121099320</v>
       </c>
       <c r="B14" t="n">
-        <v>79724</v>
+        <v>79689</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2086,45 +2085,45 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lillmyren, Lillmyren, Jmt</t>
+          <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510487</v>
+        <v>510339</v>
       </c>
       <c r="R14" t="n">
-        <v>7001652</v>
+        <v>7001763</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2209,10 +2208,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121156685</v>
+        <v>121098825</v>
       </c>
       <c r="B15" t="n">
-        <v>57370</v>
+        <v>91407</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2221,53 +2220,52 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>67</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lillmyren, Jmt</t>
+          <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510480</v>
+        <v>510388</v>
       </c>
       <c r="R15" t="n">
-        <v>7001661</v>
+        <v>7001745</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2299,17 +2297,13 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska hackspår av spillkråka i basen av en levande granstam och i en kolad stubbe.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2330,12 +2324,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Både med och utan markkontakt. Delen av stammen där sprickporingens fruktkroppar växer ligger ca 2 dm över marken. # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2353,10 +2347,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121156706</v>
+        <v>121156685</v>
       </c>
       <c r="B16" t="n">
-        <v>90713</v>
+        <v>57371</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2369,40 +2363,49 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Porten, Jmt</t>
+          <t>Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510388</v>
+        <v>510480</v>
       </c>
       <c r="R16" t="n">
-        <v>7001745</v>
+        <v>7001661</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2434,13 +2437,17 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska hackspår av spillkråka i basen av en levande granstam och i en kolad stubbe.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2461,12 +2468,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2484,10 +2491,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121156704</v>
+        <v>121156706</v>
       </c>
       <c r="B17" t="n">
-        <v>98098</v>
+        <v>90719</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2496,58 +2503,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lillmyren, Jmt</t>
+          <t>Porten, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510486</v>
+        <v>510388</v>
       </c>
       <c r="R17" t="n">
-        <v>7001664</v>
+        <v>7001745</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2582,11 +2572,6 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Minst 170 st. skott/stjälkar och 6 st. fröställningar av knärot inom ca 1 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2602,9 +2587,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>På frisk och frisk-fuktig mark.</t>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2622,10 +2622,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121097723</v>
+        <v>121098269</v>
       </c>
       <c r="B18" t="n">
-        <v>95645</v>
+        <v>79725</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2634,31 +2634,34 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>6464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2666,10 +2669,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>510506</v>
+        <v>510487</v>
       </c>
       <c r="R18" t="n">
-        <v>7001644</v>
+        <v>7001652</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2717,6 +2720,26 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2734,10 +2757,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121099320</v>
+        <v>121099463</v>
       </c>
       <c r="B19" t="n">
-        <v>79688</v>
+        <v>79718</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2746,32 +2769,32 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2781,10 +2804,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>510339</v>
+        <v>510317</v>
       </c>
       <c r="R19" t="n">
-        <v>7001763</v>
+        <v>7001784</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2869,10 +2892,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121099463</v>
+        <v>121097723</v>
       </c>
       <c r="B20" t="n">
-        <v>79717</v>
+        <v>95651</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2881,45 +2904,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Porten, Porten, Jmt</t>
+          <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>510317</v>
+        <v>510506</v>
       </c>
       <c r="R20" t="n">
-        <v>7001784</v>
+        <v>7001644</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2967,26 +2987,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3004,10 +3004,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121099241</v>
+        <v>121099111</v>
       </c>
       <c r="B21" t="n">
-        <v>78607</v>
+        <v>98104</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3016,41 +3016,58 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>510337</v>
+        <v>510355</v>
       </c>
       <c r="R21" t="n">
-        <v>7001780</v>
+        <v>7001742</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3115,10 +3132,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121098578</v>
+        <v>121099210</v>
       </c>
       <c r="B22" t="n">
-        <v>95645</v>
+        <v>90684</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3127,31 +3144,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3159,10 +3175,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>510428</v>
+        <v>510364</v>
       </c>
       <c r="R22" t="n">
-        <v>7001712</v>
+        <v>7001767</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3210,16 +3226,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3237,10 +3243,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121099111</v>
+        <v>121098983</v>
       </c>
       <c r="B23" t="n">
-        <v>98098</v>
+        <v>90733</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3249,58 +3255,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>510355</v>
+        <v>510387</v>
       </c>
       <c r="R23" t="n">
-        <v>7001742</v>
+        <v>7001741</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3348,6 +3337,16 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3365,10 +3364,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121099213</v>
+        <v>121099162</v>
       </c>
       <c r="B24" t="n">
-        <v>78607</v>
+        <v>57508</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3381,37 +3380,50 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>510360</v>
+        <v>510354</v>
       </c>
       <c r="R24" t="n">
-        <v>7001779</v>
+        <v>7001746</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3452,7 +3464,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3476,10 +3487,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121098790</v>
+        <v>121099213</v>
       </c>
       <c r="B25" t="n">
-        <v>95645</v>
+        <v>78608</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3492,27 +3503,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3520,10 +3530,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>510395</v>
+        <v>510360</v>
       </c>
       <c r="R25" t="n">
-        <v>7001752</v>
+        <v>7001779</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3570,17 +3580,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3598,10 +3598,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121099190</v>
+        <v>121098578</v>
       </c>
       <c r="B26" t="n">
-        <v>98098</v>
+        <v>95651</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3610,58 +3610,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>510363</v>
+        <v>510428</v>
       </c>
       <c r="R26" t="n">
-        <v>7001774</v>
+        <v>7001712</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3709,6 +3693,16 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3726,10 +3720,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121099090</v>
+        <v>121098790</v>
       </c>
       <c r="B27" t="n">
-        <v>98098</v>
+        <v>95651</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3738,58 +3732,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>510375</v>
+        <v>510395</v>
       </c>
       <c r="R27" t="n">
-        <v>7001739</v>
+        <v>7001752</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3836,7 +3814,17 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3854,10 +3842,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121098983</v>
+        <v>121099190</v>
       </c>
       <c r="B28" t="n">
-        <v>90727</v>
+        <v>98104</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3866,41 +3854,58 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>510387</v>
+        <v>510363</v>
       </c>
       <c r="R28" t="n">
-        <v>7001741</v>
+        <v>7001774</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3948,16 +3953,6 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3975,10 +3970,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121099891</v>
+        <v>121099241</v>
       </c>
       <c r="B29" t="n">
-        <v>79689</v>
+        <v>78608</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3991,21 +3986,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4018,10 +4013,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>510301</v>
+        <v>510337</v>
       </c>
       <c r="R29" t="n">
-        <v>7001726</v>
+        <v>7001780</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4069,21 +4064,6 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4104,7 +4084,7 @@
         <v>121098783</v>
       </c>
       <c r="B30" t="n">
-        <v>90999</v>
+        <v>91005</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4232,10 +4212,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121099210</v>
+        <v>121099891</v>
       </c>
       <c r="B31" t="n">
-        <v>90678</v>
+        <v>79690</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4244,25 +4224,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4275,10 +4255,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>510364</v>
+        <v>510301</v>
       </c>
       <c r="R31" t="n">
-        <v>7001767</v>
+        <v>7001726</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4326,6 +4306,21 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4343,10 +4338,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121099277</v>
+        <v>121099090</v>
       </c>
       <c r="B32" t="n">
-        <v>74713</v>
+        <v>98104</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4355,41 +4350,58 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>510345</v>
+        <v>510375</v>
       </c>
       <c r="R32" t="n">
-        <v>7001762</v>
+        <v>7001739</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4437,21 +4449,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4469,10 +4466,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121099162</v>
+        <v>121099277</v>
       </c>
       <c r="B33" t="n">
-        <v>57507</v>
+        <v>74714</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4485,50 +4482,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>510354</v>
+        <v>510345</v>
       </c>
       <c r="R33" t="n">
-        <v>7001746</v>
+        <v>7001762</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4569,12 +4553,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>

--- a/artfynd/A 50126-2024 artfynd.xlsx
+++ b/artfynd/A 50126-2024 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>121097256</v>
       </c>
       <c r="B4" t="n">
-        <v>57354</v>
+        <v>57487</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -989,6 +989,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,7 +1048,7 @@
         <v>121097307</v>
       </c>
       <c r="B5" t="n">
-        <v>57354</v>
+        <v>57487</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1124,6 +1129,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1799,7 +1809,7 @@
         <v>121156694</v>
       </c>
       <c r="B12" t="n">
-        <v>57355</v>
+        <v>57487</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1884,6 +1894,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 50126-2024 artfynd.xlsx
+++ b/artfynd/A 50126-2024 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>121097256</v>
       </c>
       <c r="B4" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>121097307</v>
       </c>
       <c r="B5" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>121156694</v>
       </c>
       <c r="B12" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 50126-2024 artfynd.xlsx
+++ b/artfynd/A 50126-2024 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>121097256</v>
       </c>
       <c r="B4" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>121097307</v>
       </c>
       <c r="B5" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>121156694</v>
       </c>
       <c r="B12" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 50126-2024 artfynd.xlsx
+++ b/artfynd/A 50126-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91797690</v>
+        <v>121097723</v>
       </c>
       <c r="B2" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1503</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kullen, Jmt</t>
+          <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510308.8491866561</v>
+        <v>510506</v>
       </c>
       <c r="R2" t="n">
-        <v>7001870.755532118</v>
+        <v>7001644</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,45 +758,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AN2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sebastian Acker</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sebastian Acker</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121097263</v>
+        <v>121098578</v>
       </c>
       <c r="B3" t="n">
-        <v>79688</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,34 +793,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillmyren, Lillmyren, Jmt</t>
+          <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510522</v>
+        <v>510428</v>
       </c>
       <c r="R3" t="n">
-        <v>7001662</v>
+        <v>7001712</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,8 +865,24 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -905,15 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121097256</v>
+        <v>121098790</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -921,42 +910,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lillmyren, Lillmyren, Jmt</t>
+          <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510522</v>
+        <v>510395</v>
       </c>
       <c r="R4" t="n">
-        <v>7001662</v>
+        <v>7001752</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,43 +976,29 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en tall.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1045,58 +1016,56 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121097307</v>
+        <v>121098825</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92637</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillmyren, Lillmyren, Jmt</t>
+          <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>510514</v>
+        <v>510388</v>
       </c>
       <c r="R5" t="n">
-        <v>7001648</v>
+        <v>7001745</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,17 +1100,13 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1162,12 +1127,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Både med och utan markkontakt. Delen av stammen där sprickporingens fruktkroppar växer ligger ca 2 dm över marken. # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1185,15 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121097354</v>
+        <v>121098199</v>
       </c>
       <c r="B6" t="n">
-        <v>90731</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,21 +1161,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1225,10 +1185,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510507</v>
+        <v>510513</v>
       </c>
       <c r="R6" t="n">
-        <v>7001641</v>
+        <v>7001652</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1287,15 +1247,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121098323</v>
+        <v>121098783</v>
       </c>
       <c r="B7" t="n">
-        <v>74713</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1303,34 +1258,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lillmyren, Lillmyren, Jmt</t>
+          <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510503</v>
+        <v>510388</v>
       </c>
       <c r="R7" t="n">
-        <v>7001630</v>
+        <v>7001741</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1371,8 +1329,34 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1389,53 +1373,52 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121098199</v>
+        <v>91797687</v>
       </c>
       <c r="B8" t="n">
-        <v>90999</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>760</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lillmyren, Lillmyren, Jmt</t>
+          <t>Kullen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510513</v>
+        <v>510286</v>
       </c>
       <c r="R8" t="n">
-        <v>7001652</v>
+        <v>7001771</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1459,12 +1442,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2020-07-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2020-07-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,66 +1458,84 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Sebastian Acker</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121098265</v>
+        <v>121099827</v>
       </c>
       <c r="B9" t="n">
-        <v>79688</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lillmyren, Lillmyren, Jmt</t>
+          <t>Kullen, Kullen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510510</v>
+        <v>510357</v>
       </c>
       <c r="R9" t="n">
-        <v>7001653</v>
+        <v>7001834</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1575,8 +1576,39 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>En smalväxt sälg.</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Salix caprea # En smalväxt sälg.</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1593,15 +1625,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121097284</v>
+        <v>121156706</v>
       </c>
       <c r="B10" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1609,43 +1636,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lillmyren, Lillmyren, Jmt</t>
+          <t>Porten, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510508</v>
+        <v>510388</v>
       </c>
       <c r="R10" t="n">
-        <v>7001663</v>
+        <v>7001745</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,8 +1707,34 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1704,50 +1751,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121099202</v>
+        <v>121098983</v>
       </c>
       <c r="B11" t="n">
-        <v>78343</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510360</v>
+        <v>510387</v>
       </c>
       <c r="R11" t="n">
-        <v>7001779</v>
+        <v>7001741</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,8 +1833,24 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1806,65 +1867,52 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121156694</v>
+        <v>91797690</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillmyren, Jmt</t>
+          <t>Kullen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510480</v>
+        <v>510309</v>
       </c>
       <c r="R12" t="n">
-        <v>7001661</v>
+        <v>7001871</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1888,17 +1936,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2020-07-14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>2020-07-14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,110 +1953,75 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
+      <c r="AN12" t="n">
+        <v>1</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>1 substratenheter</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Sebastian Acker</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121156704</v>
+        <v>121099891</v>
       </c>
       <c r="B13" t="n">
-        <v>98104</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lillmyren, Jmt</t>
+          <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510486</v>
+        <v>510301</v>
       </c>
       <c r="R13" t="n">
-        <v>7001664</v>
+        <v>7001726</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2048,11 +2056,6 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Minst 170 st. skott/stjälkar och 6 st. fröställningar av knärot inom ca 1 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2068,9 +2071,19 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>På frisk och frisk-fuktig mark.</t>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2088,15 +2101,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121099320</v>
+        <v>121099339</v>
       </c>
       <c r="B14" t="n">
-        <v>79689</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,30 +2112,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2135,10 +2139,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510339</v>
+        <v>510302</v>
       </c>
       <c r="R14" t="n">
-        <v>7001763</v>
+        <v>7001784</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2186,26 +2190,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2223,49 +2207,36 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121098825</v>
+        <v>121099210</v>
       </c>
       <c r="B15" t="n">
-        <v>91407</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>67</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2274,10 +2245,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510388</v>
+        <v>510364</v>
       </c>
       <c r="R15" t="n">
-        <v>7001745</v>
+        <v>7001767</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2325,26 +2296,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Både med och utan markkontakt. Delen av stammen där sprickporingens fruktkroppar växer ligger ca 2 dm över marken. # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2362,65 +2313,51 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121156685</v>
+        <v>121099213</v>
       </c>
       <c r="B16" t="n">
-        <v>57371</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lillmyren, Jmt</t>
+          <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510480</v>
+        <v>510360</v>
       </c>
       <c r="R16" t="n">
-        <v>7001661</v>
+        <v>7001779</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2452,43 +2389,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska hackspår av spillkråka i basen av en levande granstam och i en kolad stubbe.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2506,37 +2419,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121156706</v>
+        <v>121099241</v>
       </c>
       <c r="B17" t="n">
-        <v>90719</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2545,14 +2453,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Porten, Jmt</t>
+          <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510388</v>
+        <v>510337</v>
       </c>
       <c r="R17" t="n">
-        <v>7001745</v>
+        <v>7001780</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2600,26 +2508,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2637,57 +2525,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121098269</v>
+        <v>121098323</v>
       </c>
       <c r="B18" t="n">
-        <v>79725</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>510487</v>
+        <v>510503</v>
       </c>
       <c r="R18" t="n">
-        <v>7001652</v>
+        <v>7001630</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2728,34 +2604,8 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2772,46 +2622,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121099463</v>
+        <v>121099277</v>
       </c>
       <c r="B19" t="n">
-        <v>79718</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2819,10 +2660,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>510317</v>
+        <v>510345</v>
       </c>
       <c r="R19" t="n">
-        <v>7001784</v>
+        <v>7001762</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2874,22 +2715,17 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2907,15 +2743,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121097723</v>
+        <v>121099202</v>
       </c>
       <c r="B20" t="n">
-        <v>95651</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2923,38 +2754,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lillmyren, Lillmyren, Jmt</t>
+          <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>510506</v>
+        <v>510360</v>
       </c>
       <c r="R20" t="n">
-        <v>7001644</v>
+        <v>7001779</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2995,14 +2822,8 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3019,73 +2840,52 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121099111</v>
+        <v>91797689</v>
       </c>
       <c r="B21" t="n">
-        <v>98104</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Porten, Porten, Jmt</t>
+          <t>Kullen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>510355</v>
+        <v>510302</v>
       </c>
       <c r="R21" t="n">
-        <v>7001742</v>
+        <v>7001798</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3109,12 +2909,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2020-07-14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2020-07-14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3123,80 +2923,82 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
+      <c r="AN21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Sebastian Acker</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121099210</v>
+        <v>91797688</v>
       </c>
       <c r="B22" t="n">
-        <v>90684</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Porten, Porten, Jmt</t>
+          <t>Kullen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>510364</v>
+        <v>510295</v>
       </c>
       <c r="R22" t="n">
-        <v>7001767</v>
+        <v>7001790</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3220,12 +3022,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2020-07-14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2020-07-14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3234,39 +3036,40 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
+      <c r="AN22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Sebastian Acker</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121098983</v>
+        <v>121097263</v>
       </c>
       <c r="B23" t="n">
-        <v>90733</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3274,37 +3077,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Porten, Porten, Jmt</t>
+          <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>510387</v>
+        <v>510522</v>
       </c>
       <c r="R23" t="n">
-        <v>7001741</v>
+        <v>7001662</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3345,24 +3145,8 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3379,15 +3163,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121099162</v>
+        <v>121098265</v>
       </c>
       <c r="B24" t="n">
-        <v>57508</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3395,50 +3174,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Porten, Porten, Jmt</t>
+          <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>510354</v>
+        <v>510510</v>
       </c>
       <c r="R24" t="n">
-        <v>7001746</v>
+        <v>7001653</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3481,11 +3244,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3502,15 +3260,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121099213</v>
+        <v>121099320</v>
       </c>
       <c r="B25" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3518,26 +3271,30 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3545,10 +3302,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>510360</v>
+        <v>510339</v>
       </c>
       <c r="R25" t="n">
-        <v>7001779</v>
+        <v>7001763</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3596,6 +3353,26 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3613,43 +3390,41 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121098578</v>
+        <v>121099463</v>
       </c>
       <c r="B26" t="n">
-        <v>95651</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3657,10 +3432,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>510428</v>
+        <v>510317</v>
       </c>
       <c r="R26" t="n">
-        <v>7001712</v>
+        <v>7001784</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3710,14 +3485,24 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3735,54 +3520,52 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121098790</v>
+        <v>121098269</v>
       </c>
       <c r="B27" t="n">
-        <v>95651</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>53</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Porten, Porten, Jmt</t>
+          <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>510395</v>
+        <v>510487</v>
       </c>
       <c r="R27" t="n">
-        <v>7001752</v>
+        <v>7001652</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3829,17 +3612,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3857,55 +3650,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121099190</v>
+        <v>121156685</v>
       </c>
       <c r="B28" t="n">
-        <v>98104</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3913,17 +3693,17 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Porten, Porten, Jmt</t>
+          <t>Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>510363</v>
+        <v>510480</v>
       </c>
       <c r="R28" t="n">
-        <v>7001774</v>
+        <v>7001661</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3955,19 +3735,43 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska hackspår av spillkråka i basen av en levande granstam och i en kolad stubbe.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3985,15 +3789,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121099241</v>
+        <v>121097256</v>
       </c>
       <c r="B29" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4001,37 +3800,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Porten, Porten, Jmt</t>
+          <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>510337</v>
+        <v>510522</v>
       </c>
       <c r="R29" t="n">
-        <v>7001780</v>
+        <v>7001662</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4066,19 +3870,43 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en tall.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4096,15 +3924,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121098783</v>
+        <v>121097307</v>
       </c>
       <c r="B30" t="n">
-        <v>91005</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4112,37 +3935,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Porten, Porten, Jmt</t>
+          <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>510388</v>
+        <v>510514</v>
       </c>
       <c r="R30" t="n">
-        <v>7001741</v>
+        <v>7001648</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4177,19 +4005,23 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4204,12 +4036,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4227,15 +4059,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121099891</v>
+        <v>121156694</v>
       </c>
       <c r="B31" t="n">
-        <v>79690</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4243,40 +4070,49 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Porten, Porten, Jmt</t>
+          <t>Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>510301</v>
+        <v>510480</v>
       </c>
       <c r="R31" t="n">
-        <v>7001726</v>
+        <v>7001661</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4308,13 +4144,17 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4325,17 +4165,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4353,70 +4198,54 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121099090</v>
+        <v>121097284</v>
       </c>
       <c r="B32" t="n">
-        <v>98104</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Porten, Porten, Jmt</t>
+          <t>Lillmyren, Lillmyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>510375</v>
+        <v>510508</v>
       </c>
       <c r="R32" t="n">
-        <v>7001739</v>
+        <v>7001663</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4457,14 +4286,8 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4481,15 +4304,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121099277</v>
+        <v>121099162</v>
       </c>
       <c r="B33" t="n">
-        <v>74714</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4497,37 +4315,50 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Porten, Porten, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>510345</v>
+        <v>510354</v>
       </c>
       <c r="R33" t="n">
-        <v>7001762</v>
+        <v>7001746</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4568,28 +4399,12 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4604,6 +4419,508 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>121099090</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Porten, Porten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>510375</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7001739</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>121099111</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Porten, Porten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>510355</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7001742</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>121099190</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Porten, Porten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>510363</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7001774</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>121156704</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lillmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>510486</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7001664</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Minst 170 st. skott/stjälkar och 6 st. fröställningar av knärot inom ca 1 m2 yta.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>På frisk och frisk-fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50126-2024 artfynd.xlsx
+++ b/artfynd/A 50126-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121097723</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121098578</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121098790</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1147,6 +1167,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121098825</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1244,6 +1269,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121098199</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1370,6 +1400,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121098783</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1483,6 +1518,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91797687</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1622,6 +1662,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121099827</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1748,6 +1793,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121156706</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1864,6 +1914,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121098983</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1975,6 +2030,11 @@
       <c r="AY12" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91797690</t>
         </is>
       </c>
     </row>
@@ -2098,6 +2158,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121099891</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2204,6 +2269,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121099339</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2310,6 +2380,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121099210</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2416,6 +2491,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121099213</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2522,6 +2602,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121099241</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2619,6 +2704,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121098323</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2740,6 +2830,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121099277</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2837,6 +2932,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121099202</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2950,6 +3050,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91797689</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3063,6 +3168,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91797688</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3160,6 +3270,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121097263</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3257,6 +3372,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121098265</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3387,6 +3507,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121099320</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3517,6 +3642,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121099463</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3647,6 +3777,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121098269</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3786,6 +3921,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121156685</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3921,6 +4061,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121097256</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4056,6 +4201,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121097307</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4195,6 +4345,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121156694</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4301,6 +4456,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121097284</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4419,6 +4579,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121099162</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4542,6 +4707,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121099090</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4665,6 +4835,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121099111</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4788,6 +4963,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121099190</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4921,8 +5101,51 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121156704</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>